--- a/data/trans_orig/P13A_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310463</t>
+          <t>310585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281343</t>
+          <t>281402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287728</t>
+          <t>287467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592884</t>
+          <t>592622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598998</t>
+          <t>598953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495097</t>
+          <t>495323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512241</t>
+          <t>511994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479038</t>
+          <t>479102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495877</t>
+          <t>496410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>981164</t>
+          <t>979766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004717</t>
+          <t>1004112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303281</t>
+          <t>303051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311725</t>
+          <t>311647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>322023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335570</t>
+          <t>335002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629153</t>
+          <t>629171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644464</t>
+          <t>644717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33013</t>
+          <t>34964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305829</t>
+          <t>305726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311296</t>
+          <t>311305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443041</t>
+          <t>442935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465562</t>
+          <t>465827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753469</t>
+          <t>751518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774997</t>
+          <t>775544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>170086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201306</t>
+          <t>200462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206503</t>
+          <t>206498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375801</t>
+          <t>375763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383891</t>
+          <t>384301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258098</t>
+          <t>257758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266160</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237806</t>
+          <t>238670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248692</t>
+          <t>248794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499686</t>
+          <t>501005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513160</t>
+          <t>513371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56937</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>62749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600670</t>
+          <t>602540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613271</t>
+          <t>613377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>788630</t>
+          <t>788704</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>827576</t>
+          <t>826921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1399779</t>
+          <t>1399495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1434022</t>
+          <t>1431485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>45247</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>922210</t>
+          <t>922147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>669877</t>
+          <t>672303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698042</t>
+          <t>698293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1597405</t>
+          <t>1595257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1626779</t>
+          <t>1626984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118711</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>173404</t>
+          <t>172756</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>153163</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211370</t>
+          <t>211769</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3396281</t>
+          <t>3396675</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3422966</t>
+          <t>3422865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3474944</t>
+          <t>3475592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529637</t>
+          <t>3532211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6885046</t>
+          <t>6884647</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6943743</t>
+          <t>6943253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311273</t>
+          <t>317698</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310585</t>
+          <t>313044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>285335</t>
+          <t>311248</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281402</t>
+          <t>306877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287467</t>
+          <t>313577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>596607</t>
+          <t>628946</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592622</t>
+          <t>623546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598953</t>
+          <t>631974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505341</t>
+          <t>517476</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495323</t>
+          <t>506920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511994</t>
+          <t>524067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>488314</t>
+          <t>518844</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479102</t>
+          <t>508920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496410</t>
+          <t>526952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>993655</t>
+          <t>1036320</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>979766</t>
+          <t>1021920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004112</t>
+          <t>1047255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308587</t>
+          <t>308641</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303051</t>
+          <t>303421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311647</t>
+          <t>311871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>329462</t>
+          <t>335116</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322023</t>
+          <t>327019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335002</t>
+          <t>341437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>638048</t>
+          <t>643757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629171</t>
+          <t>633614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644717</t>
+          <t>650155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309800</t>
+          <t>370322</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305726</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311305</t>
+          <t>371812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>457472</t>
+          <t>401350</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442935</t>
+          <t>386879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465827</t>
+          <t>409715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>767272</t>
+          <t>771672</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751518</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>775544</t>
+          <t>780156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176718</t>
+          <t>203617</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170086</t>
+          <t>196920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>204413</t>
+          <t>222716</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200462</t>
+          <t>219168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206498</t>
+          <t>225001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>381131</t>
+          <t>426333</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375763</t>
+          <t>421215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384301</t>
+          <t>429493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,22 +2440,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>26759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>263114</t>
+          <t>264188</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257758</t>
+          <t>258737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266200</t>
+          <t>267245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>244390</t>
+          <t>251026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238670</t>
+          <t>244531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248794</t>
+          <t>255508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>507504</t>
+          <t>515215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501005</t>
+          <t>506951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513371</t>
+          <t>520741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,22 +2783,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>37258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56863</t>
+          <t>61874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62749</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>609157</t>
+          <t>701379</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602540</t>
+          <t>693883</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613377</t>
+          <t>706424</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>805533</t>
+          <t>716932</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>788704</t>
+          <t>703477</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826921</t>
+          <t>728093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1414689</t>
+          <t>1418310</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1399495</t>
+          <t>1402615</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1431485</t>
+          <t>1430063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3239,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>926687</t>
+          <t>795786</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>922147</t>
+          <t>790489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>689936</t>
+          <t>804804</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>672303</t>
+          <t>794799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698293</t>
+          <t>811568</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1616623</t>
+          <t>1600590</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1595257</t>
+          <t>1589556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1626984</t>
+          <t>1607761</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116137</t>
+          <t>135676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>172756</t>
+          <t>179204</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>153163</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211769</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3410675</t>
+          <t>3479108</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3396675</t>
+          <t>3463463</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3422865</t>
+          <t>3489747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3504855</t>
+          <t>3562037</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3475592</t>
+          <t>3537914</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3532211</t>
+          <t>3581442</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6915529</t>
+          <t>7041145</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6884647</t>
+          <t>7013646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6943253</t>
+          <t>7067934</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
